--- a/main/4_16kHz_Data/all_sessions_labels.xlsx
+++ b/main/4_16kHz_Data/all_sessions_labels.xlsx
@@ -464,17 +464,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Trial_Type</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Action_choice</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Reward</t>
         </is>
       </c>
     </row>
@@ -5665,17 +5665,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Trial_Type</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Action_choice</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Reward</t>
         </is>
       </c>
     </row>
@@ -10141,17 +10141,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Trial_Type</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Action_choice</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Reward</t>
         </is>
       </c>
     </row>
@@ -15742,17 +15742,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Trial_Type</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Action_choice</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Reward</t>
         </is>
       </c>
     </row>
@@ -21038,12 +21038,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>ROIs</t>
+          <t>Cells</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Timepoints</t>
+          <t>Frames</t>
         </is>
       </c>
     </row>
@@ -21338,7 +21338,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Trial_Type</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -21357,7 +21357,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Action_choice</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -21376,7 +21376,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -21429,17 +21429,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Trial_Type</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Action_choice</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Reward</t>
         </is>
       </c>
     </row>
@@ -26780,17 +26780,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Trial_Type</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Action_choice</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Reward</t>
         </is>
       </c>
     </row>
@@ -32581,17 +32581,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Trial_Type</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Action_choice</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Reward</t>
         </is>
       </c>
     </row>
@@ -37682,17 +37682,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Trial_Type</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Action_choice</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Reward</t>
         </is>
       </c>
     </row>
@@ -42908,17 +42908,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Trial_Type</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Action_choice</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Reward</t>
         </is>
       </c>
     </row>
@@ -48259,17 +48259,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Trial_Type</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Action_choice</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Reward</t>
         </is>
       </c>
     </row>
@@ -54910,17 +54910,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Trial_Type</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Action_choice</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Reward</t>
         </is>
       </c>
     </row>
@@ -60736,17 +60736,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Trial_Type</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Action_choice</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Reward</t>
         </is>
       </c>
     </row>
